--- a/Excel/11-div22q4.xlsx
+++ b/Excel/11-div22q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\Local\Packages\oice_16_974fa576_32c1d314_2701\AC\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{B16C07FF-7D9A-49DB-9D95-96F12495ED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29B0A3C4-B65D-44DC-8391-CB4FB95E925C}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{B16C07FF-7D9A-49DB-9D95-96F12495ED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63AB4115-DDA1-4473-A7F6-659A15BA82B3}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1059,7 +1059,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.75">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="11">
@@ -1091,7 +1091,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="11">
@@ -1123,7 +1123,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="18.75">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
@@ -1155,7 +1155,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="18.75">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="11">
@@ -1187,7 +1187,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="18.75">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="11">
@@ -1219,7 +1219,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="18.75">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="11">
@@ -1251,7 +1251,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="18.75">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="11">
@@ -1283,7 +1283,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="18.75">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="11">
@@ -1315,7 +1315,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="18.75">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="11">
@@ -1347,7 +1347,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="18.75">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="11">
@@ -1379,7 +1379,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="18.75">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="11">
@@ -1411,7 +1411,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="18.75">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="11">
@@ -1443,7 +1443,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="18.75">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="11">
@@ -1475,7 +1475,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="18.75">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="11">
@@ -1507,7 +1507,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="18.75">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="11">
@@ -1539,7 +1539,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="18.75">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="11">
@@ -1571,7 +1571,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="18.75">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="11">
@@ -1603,7 +1603,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="18.75">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="11">
@@ -1635,7 +1635,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="18.75">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="11">
@@ -1667,7 +1667,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="18.75">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="11">
@@ -1699,7 +1699,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="18.75">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="11">
@@ -1731,7 +1731,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="18.75">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="11">
@@ -1763,7 +1763,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="11">
@@ -1795,7 +1795,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="18.75">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="11">
@@ -1827,7 +1827,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="18.75">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="11">
@@ -1859,7 +1859,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="18.75">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="11">

--- a/Excel/11-div22q4.xlsx
+++ b/Excel/11-div22q4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\Local\Packages\oice_16_974fa576_32c1d314_2701\AC\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{B16C07FF-7D9A-49DB-9D95-96F12495ED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63AB4115-DDA1-4473-A7F6-659A15BA82B3}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{B16C07FF-7D9A-49DB-9D95-96F12495ED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F453BF01-26C6-45E6-A623-D6668BA17122}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1226,7 +1226,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="C7" s="12">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="D7" s="13">
         <v>3900</v>
